--- a/Employee_Reports_wi48/James Andrew Aquino Rodillo Q0546.xlsx
+++ b/Employee_Reports_wi48/James Andrew Aquino Rodillo Q0546.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-80</v>
+        <v>-83</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1301,11 +1301,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-333</v>
+        <v>-336</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1350,11 +1350,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-123</v>
+        <v>-126</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1399,11 +1399,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-144</v>
+        <v>-147</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1422,9 +1422,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
           <t>17-Mar-2025</t>
@@ -1436,11 +1448,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-118</v>
+        <v>-121</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1485,11 +1497,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-31</v>
+        <v>-34</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1534,11 +1546,11 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1583,11 +1595,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1632,11 +1644,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1681,11 +1693,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1730,11 +1742,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1767,11 +1779,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1804,11 +1816,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1841,11 +1853,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
